--- a/templates/PRAP_SourceData_Dummy_v1.10.xlsx
+++ b/templates/PRAP_SourceData_Dummy_v1.10.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A120"/>
+  <dimension ref="A1:A128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1088,28 +1088,28 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>ADDING A PERMITTED VALUE</t>
+          <t>ASSIGNMENT DATES ARE OPTIONAL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
+          <t xml:space="preserve">   Leave assign_start_date and assign_end_date BLANK for somebody who is on the project for</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
+          <t xml:space="preserve">   the whole of it - which is most people. A blank date means the project's own, so the two</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
+          <t xml:space="preserve">   never fall out of step when the project's dates move.</t>
         </is>
       </c>
     </row>
@@ -1117,211 +1117,259 @@
       <c r="A87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fill them in only for a PARTIAL involvement: somebody who joins late, leaves early, or</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PeriodWeightStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
+          <t xml:space="preserve">   covers one stretch of a longer study.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ADDING A PERMITTED VALUE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
+          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
+          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
+          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the same thing three times.</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr"/>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IS IN THIS FILE</t>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PeriodWeightStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   62 projects   50 clinical trials (PRJ-001..050) + 12 'Others' (PRJ-051..062)</t>
+          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   20 people     PSN-001..020, including two part-timers (PSN-004 at 0.80,</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 PSN-020 at 0.60 capacity)</t>
+          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   289 assignments, 372 milestones, 308 periods, spanning 73 months</t>
+          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Trials are spread evenly across Phase 1-4 and staggered from 2025 to 2031.</t>
+          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr"/>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the same thing three times.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IT DEMONSTRATES</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 30 trials carry an interim DB lock, so each has TWO 'Conduct' stretches and two</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>WHAT IS IN THIS FILE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     close-out periods. The other 20 run Conduct once.</t>
+          <t xml:space="preserve">   62 projects   50 clinical trials (PRJ-001..050) + 12 'Others' (PRJ-051..062)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 12 trials record an 'Inspection' after the final DB lock and so carry the seventh</t>
+          <t xml:space="preserve">   20 people     PSN-001..020, including two part-timers (PSN-004 at 0.80,</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     period, 'After Close-out (final)'.</t>
+          <t xml:space="preserve">                 PSN-020 at 0.60 capacity)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - The 12 'Others' projects have hand-entered periods and no milestones.</t>
+          <t xml:space="preserve">   289 assignments, 372 milestones, 308 periods, spanning 73 months</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - PSN-001 is pushed above the 1.50 FTE ceiling for a stretch in 2026-27.</t>
+          <t xml:space="preserve">   Trials are spread evenly across Phase 1-4 and staggered from 2025 to 2031.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - PSN-020 is a part-timer (0.60 FTE) carrying one light assignment, so an under-allocation run</t>
-        </is>
-      </c>
+      <c r="A111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     is raised. With the floor now at 0.60 (S2-05) they CAN clear it, but only at full</t>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>WHAT IT DEMONSTRATES</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     utilisation - V-22 warns if anyone is recorded below the floor and so could never clear it.</t>
+          <t xml:space="preserve">   - 30 trials carry an interim DB lock, so each has TWO 'Conduct' stretches and two</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Two assignments carry PersonPeriodWeight overrides.</t>
+          <t xml:space="preserve">     close-out periods. The other 20 run Conduct once.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr"/>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 12 trials record an 'Inspection' after the final DB lock and so carry the seventh</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Typical load is around 0.93 FTE per person-month (median). Months at the very start</t>
+          <t xml:space="preserve">     period, 'After Close-out (final)'.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and end of the 73-month span are naturally light, since few projects overlap there.</t>
+          <t xml:space="preserve">   - The 12 'Others' projects have hand-entered periods and no milestones.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr"/>
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - PSN-001 is pushed above the 1.50 FTE ceiling for a stretch in 2026-27.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The weights and role factors here are ILLUSTRATIVE, so the numbers can be exercised.</t>
+          <t xml:space="preserve">   - PSN-020 is a part-timer (0.60 FTE) carrying one light assignment, so an under-allocation run</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     is raised. With the floor now at 0.60 (S2-05) they CAN clear it, but only at full</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     utilisation - V-22 warns if anyone is recorded below the floor and so could never clear it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Two assignments carry PersonPeriodWeight overrides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Typical load is around 0.93 FTE per person-month (median). Months at the very start</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   and end of the 73-month span are naturally light, since few projects overlap there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The weights and role factors here are ILLUSTRATIVE, so the numbers can be exercised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Replace them with your own before drawing any conclusion from the output.</t>
         </is>
@@ -70358,14 +70406,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n">
-        <v>46753</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>47634</v>
-      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
       <c r="H2" s="7" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="n"/>
@@ -70472,14 +70516,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>46722</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>47603</v>
-      </c>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
       <c r="H5" s="7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
@@ -70511,13 +70551,13 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46722</v>
+        <v>46753</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>47634</v>
+        <v>47573</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -70549,13 +70589,13 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
@@ -70586,14 +70626,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>46477</v>
-      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
       <c r="H8" s="7" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
@@ -70625,13 +70661,13 @@
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>46477</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
@@ -70663,13 +70699,13 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
@@ -70700,14 +70736,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>46446</v>
-      </c>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
       <c r="H11" s="7" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
@@ -70739,13 +70771,13 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>46934</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
@@ -70780,10 +70812,10 @@
         <v>46113</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>46934</v>
+        <v>46965</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
@@ -70814,14 +70846,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>46965</v>
-      </c>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
       <c r="H14" s="7" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="n"/>
@@ -70853,13 +70881,13 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>46934</v>
+        <v>46965</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
@@ -70891,13 +70919,13 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>46934</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="7" t="n"/>
@@ -70928,14 +70956,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>46843</v>
-      </c>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
       <c r="H17" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
@@ -70967,13 +70991,13 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>46388</v>
+        <v>46419</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>46904</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="I18" s="7" t="n"/>
       <c r="J18" s="7" t="n"/>
@@ -71011,7 +71035,7 @@
         <v>46843</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
@@ -71042,12 +71066,8 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>46388</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>46843</v>
-      </c>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="7" t="n">
         <v>0.17</v>
       </c>
@@ -71081,13 +71101,13 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>46388</v>
+        <v>46357</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>46904</v>
+        <v>46843</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
@@ -71119,13 +71139,13 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>46476</v>
+        <v>46446</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
@@ -71156,14 +71176,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>45839</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>46446</v>
-      </c>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
       <c r="H23" s="7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
@@ -71195,13 +71211,13 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>45778</v>
+        <v>45839</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>46446</v>
+        <v>46476</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n"/>
@@ -71236,10 +71252,10 @@
         <v>45839</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>46476</v>
+        <v>46507</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
@@ -71270,14 +71286,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>45778</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>46507</v>
-      </c>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
       <c r="H26" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="n"/>
@@ -71309,7 +71321,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>47207</v>
@@ -71347,13 +71359,13 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>46508</v>
+        <v>46569</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>47207</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
@@ -71384,14 +71396,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>46539</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>47177</v>
-      </c>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
       <c r="H29" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
@@ -71426,7 +71434,7 @@
         <v>46569</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>47177</v>
+        <v>47238</v>
       </c>
       <c r="H30" s="7" t="n">
         <v>0.15</v>
@@ -71467,7 +71475,7 @@
         <v>47177</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
@@ -71498,14 +71506,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>46753</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>47542</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
       <c r="H32" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="7" t="n"/>
@@ -71537,13 +71541,13 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>46722</v>
+        <v>46692</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>47542</v>
+        <v>47572</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
@@ -71575,13 +71579,13 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>47603</v>
+        <v>47572</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="7" t="n"/>
@@ -71612,14 +71616,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
-        <v>46692</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>47542</v>
-      </c>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
       <c r="H35" s="7" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
@@ -71651,13 +71651,13 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>47572</v>
+        <v>47603</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="7" t="n"/>
@@ -71689,13 +71689,13 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>46327</v>
+        <v>46388</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>46996</v>
+        <v>47057</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
@@ -71726,14 +71726,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>47026</v>
-      </c>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
       <c r="H38" s="7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
@@ -71765,13 +71761,13 @@
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>46327</v>
+        <v>46357</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>47057</v>
+        <v>46996</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
@@ -71803,13 +71799,13 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>46388</v>
+        <v>46327</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>46996</v>
+        <v>47026</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I40" s="7" t="n"/>
       <c r="J40" s="7" t="n"/>
@@ -71840,14 +71836,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>46388</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>46996</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
       <c r="H41" s="7" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
@@ -71879,13 +71871,13 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>46783</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I42" s="7" t="n"/>
       <c r="J42" s="7" t="n"/>
@@ -71920,10 +71912,10 @@
         <v>46113</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>46812</v>
+        <v>46843</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I43" s="7" t="n"/>
       <c r="J43" s="7" t="n"/>
@@ -71954,14 +71946,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>46174</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>46783</v>
-      </c>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
       <c r="H44" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I44" s="7" t="n"/>
       <c r="J44" s="7" t="n"/>
@@ -71993,13 +71981,13 @@
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>46812</v>
+        <v>46783</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
@@ -72031,13 +72019,13 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>46812</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I46" s="7" t="n"/>
       <c r="J46" s="7" t="n"/>
@@ -72068,14 +72056,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>46965</v>
-      </c>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
       <c r="H47" s="7" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
@@ -72107,13 +72091,13 @@
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>46934</v>
+        <v>46965</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="I48" s="7" t="n"/>
       <c r="J48" s="7" t="n"/>
@@ -72145,13 +72129,13 @@
         </is>
       </c>
       <c r="F49" s="8" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>46965</v>
+        <v>46996</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I49" s="7" t="n"/>
       <c r="J49" s="7" t="n"/>
@@ -72182,12 +72166,8 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G50" s="8" t="n">
-        <v>46996</v>
-      </c>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
       <c r="H50" s="7" t="n">
         <v>0.1</v>
       </c>
@@ -72221,13 +72201,13 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>46996</v>
+        <v>46934</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="I51" s="7" t="n"/>
       <c r="J51" s="7" t="n"/>
@@ -72259,13 +72239,13 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>46599</v>
+        <v>46568</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I52" s="7" t="n"/>
       <c r="J52" s="7" t="n"/>
@@ -72296,14 +72276,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G53" s="8" t="n">
-        <v>46568</v>
-      </c>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
       <c r="H53" s="7" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I53" s="7" t="n"/>
       <c r="J53" s="7" t="n"/>
@@ -72335,13 +72311,13 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I54" s="7" t="n"/>
       <c r="J54" s="7" t="n"/>
@@ -72373,13 +72349,13 @@
         </is>
       </c>
       <c r="F55" s="8" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="G55" s="8" t="n">
         <v>46630</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I55" s="7" t="n"/>
       <c r="J55" s="7" t="n"/>
@@ -72410,14 +72386,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>46568</v>
-      </c>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
       <c r="H56" s="7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I56" s="7" t="n"/>
       <c r="J56" s="7" t="n"/>
@@ -72455,7 +72427,7 @@
         <v>47786</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I57" s="7" t="n"/>
       <c r="J57" s="7" t="n"/>
@@ -72487,13 +72459,13 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>46722</v>
+        <v>46753</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>47817</v>
+        <v>47786</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="I58" s="7" t="n"/>
       <c r="J58" s="7" t="n"/>
@@ -72524,12 +72496,8 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
-        <v>46722</v>
-      </c>
-      <c r="G59" s="8" t="n">
-        <v>47817</v>
-      </c>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
       <c r="H59" s="7" t="n">
         <v>0.13</v>
       </c>
@@ -72563,13 +72531,13 @@
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>46722</v>
+        <v>46784</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>47756</v>
+        <v>47817</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I60" s="7" t="n"/>
       <c r="J60" s="7" t="n"/>
@@ -72601,13 +72569,13 @@
         </is>
       </c>
       <c r="F61" s="8" t="n">
-        <v>46784</v>
+        <v>46753</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>47817</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I61" s="7" t="n"/>
       <c r="J61" s="7" t="n"/>
@@ -72638,14 +72606,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>46446</v>
-      </c>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
       <c r="H62" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I62" s="7" t="n"/>
       <c r="J62" s="7" t="n"/>
@@ -72677,13 +72641,13 @@
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>46476</v>
+        <v>46446</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="I63" s="7" t="n"/>
       <c r="J63" s="7" t="n"/>
@@ -72715,13 +72679,13 @@
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>46446</v>
+        <v>46476</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I64" s="7" t="n"/>
       <c r="J64" s="7" t="n"/>
@@ -72752,14 +72716,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G65" s="8" t="n">
-        <v>46446</v>
-      </c>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="8" t="n"/>
       <c r="H65" s="7" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I65" s="7" t="n"/>
       <c r="J65" s="7" t="n"/>
@@ -72794,10 +72754,10 @@
         <v>45992</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>46446</v>
+        <v>46476</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I66" s="7" t="n"/>
       <c r="J66" s="7" t="n"/>
@@ -72829,13 +72789,13 @@
         </is>
       </c>
       <c r="F67" s="8" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>46690</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I67" s="7" t="n"/>
       <c r="J67" s="7" t="n"/>
@@ -72866,14 +72826,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n">
-        <v>46204</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>46721</v>
-      </c>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="8" t="n"/>
       <c r="H68" s="7" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="I68" s="7" t="n"/>
       <c r="J68" s="7" t="n"/>
@@ -72905,13 +72861,13 @@
         </is>
       </c>
       <c r="F69" s="8" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>46721</v>
+        <v>46660</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
@@ -72949,7 +72905,7 @@
         <v>46721</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
@@ -72980,14 +72936,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n">
-        <v>46174</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>46721</v>
-      </c>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
       <c r="H71" s="7" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="n"/>
@@ -73019,10 +72971,10 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>46631</v>
+        <v>46600</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>47633</v>
+        <v>47603</v>
       </c>
       <c r="H72" s="7" t="n">
         <v>0.15</v>
@@ -73057,13 +73009,13 @@
         </is>
       </c>
       <c r="F73" s="8" t="n">
-        <v>46600</v>
+        <v>46631</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>47664</v>
+        <v>47633</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
@@ -73094,14 +73046,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n">
-        <v>46600</v>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>47664</v>
-      </c>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="8" t="n"/>
       <c r="H74" s="7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I74" s="7" t="n"/>
       <c r="J74" s="7" t="n"/>
@@ -73133,7 +73081,7 @@
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>46631</v>
+        <v>46569</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>47633</v>
@@ -73171,13 +73119,13 @@
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>46631</v>
+        <v>46569</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>47664</v>
+        <v>47633</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="n"/>
@@ -73208,14 +73156,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G77" s="8" t="n">
-        <v>46752</v>
-      </c>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
       <c r="H77" s="7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I77" s="7" t="n"/>
       <c r="J77" s="7" t="n"/>
@@ -73247,13 +73191,13 @@
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>46721</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="I78" s="7" t="n"/>
       <c r="J78" s="7" t="n"/>
@@ -73285,13 +73229,13 @@
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>46783</v>
+        <v>46752</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I79" s="7" t="n"/>
       <c r="J79" s="7" t="n"/>
@@ -73322,14 +73266,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n">
-        <v>46235</v>
-      </c>
-      <c r="G80" s="8" t="n">
-        <v>46721</v>
-      </c>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="8" t="n"/>
       <c r="H80" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I80" s="7" t="n"/>
       <c r="J80" s="7" t="n"/>
@@ -73361,13 +73301,13 @@
         </is>
       </c>
       <c r="F81" s="8" t="n">
-        <v>46296</v>
+        <v>46235</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>46721</v>
+        <v>46783</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
@@ -73399,13 +73339,13 @@
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>46844</v>
+        <v>46874</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>47876</v>
+        <v>47845</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="n"/>
@@ -73436,14 +73376,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n">
-        <v>46844</v>
-      </c>
-      <c r="G83" s="8" t="n">
-        <v>47876</v>
-      </c>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
       <c r="H83" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="n"/>
@@ -73475,13 +73411,13 @@
         </is>
       </c>
       <c r="F84" s="8" t="n">
-        <v>46844</v>
+        <v>46874</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>47876</v>
+        <v>47845</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="n"/>
@@ -73513,13 +73449,13 @@
         </is>
       </c>
       <c r="F85" s="8" t="n">
-        <v>46813</v>
+        <v>46874</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>47845</v>
+        <v>47876</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I85" s="7" t="n"/>
       <c r="J85" s="7" t="n"/>
@@ -73550,14 +73486,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F86" s="8" t="n">
-        <v>46874</v>
-      </c>
-      <c r="G86" s="8" t="n">
-        <v>47876</v>
-      </c>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="8" t="n"/>
       <c r="H86" s="7" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="I86" s="7" t="n"/>
       <c r="J86" s="7" t="n"/>
@@ -73589,13 +73521,13 @@
         </is>
       </c>
       <c r="F87" s="8" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>46873</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="I87" s="7" t="n"/>
       <c r="J87" s="7" t="n"/>
@@ -73627,13 +73559,13 @@
         </is>
       </c>
       <c r="F88" s="8" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>46812</v>
+        <v>46873</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="I88" s="7" t="n"/>
       <c r="J88" s="7" t="n"/>
@@ -73664,14 +73596,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G89" s="8" t="n">
-        <v>46812</v>
-      </c>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
       <c r="H89" s="7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I89" s="7" t="n"/>
       <c r="J89" s="7" t="n"/>
@@ -73703,13 +73631,13 @@
         </is>
       </c>
       <c r="F90" s="8" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>46873</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="n"/>
@@ -73741,13 +73669,13 @@
         </is>
       </c>
       <c r="F91" s="8" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>46842</v>
+        <v>46812</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="n"/>
@@ -73778,14 +73706,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G92" s="8" t="n">
-        <v>47299</v>
-      </c>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
       <c r="H92" s="7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="n"/>
@@ -73820,10 +73744,10 @@
         <v>46082</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>47361</v>
+        <v>47330</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I93" s="7" t="n"/>
       <c r="J93" s="7" t="n"/>
@@ -73855,13 +73779,13 @@
         </is>
       </c>
       <c r="F94" s="8" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>47361</v>
+        <v>47330</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I94" s="7" t="n"/>
       <c r="J94" s="7" t="n"/>
@@ -73892,12 +73816,8 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="G95" s="8" t="n">
-        <v>47330</v>
-      </c>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
       <c r="H95" s="7" t="n">
         <v>0.12</v>
       </c>
@@ -73937,7 +73857,7 @@
         <v>47361</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I96" s="7" t="n"/>
       <c r="J96" s="7" t="n"/>
@@ -73972,10 +73892,10 @@
         <v>45870</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>47087</v>
+        <v>47056</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I97" s="7" t="n"/>
       <c r="J97" s="7" t="n"/>
@@ -74006,14 +73926,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n">
-        <v>45809</v>
-      </c>
-      <c r="G98" s="8" t="n">
-        <v>47026</v>
-      </c>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="8" t="n"/>
       <c r="H98" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="n"/>
@@ -74045,13 +73961,13 @@
         </is>
       </c>
       <c r="F99" s="8" t="n">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="G99" s="8" t="n">
-        <v>47026</v>
+        <v>47087</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I99" s="7" t="n"/>
       <c r="J99" s="7" t="n"/>
@@ -74083,13 +73999,13 @@
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>45809</v>
+        <v>45870</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>47087</v>
+        <v>47056</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="n"/>
@@ -74120,14 +74036,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n">
-        <v>45839</v>
-      </c>
-      <c r="G101" s="8" t="n">
-        <v>47056</v>
-      </c>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
       <c r="H101" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="n"/>
@@ -74159,13 +74071,13 @@
         </is>
       </c>
       <c r="F102" s="8" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>46415</v>
+        <v>46384</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="n"/>
@@ -74197,13 +74109,13 @@
         </is>
       </c>
       <c r="F103" s="8" t="n">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="G103" s="8" t="n">
-        <v>46446</v>
+        <v>46415</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I103" s="7" t="n"/>
       <c r="J103" s="7" t="n"/>
@@ -74234,14 +74146,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F104" s="8" t="n">
-        <v>45931</v>
-      </c>
-      <c r="G104" s="8" t="n">
-        <v>46446</v>
-      </c>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="8" t="n"/>
       <c r="H104" s="7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="I104" s="7" t="n"/>
       <c r="J104" s="7" t="n"/>
@@ -74273,7 +74181,7 @@
         </is>
       </c>
       <c r="F105" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G105" s="8" t="n">
         <v>46415</v>
@@ -74311,13 +74219,13 @@
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>46415</v>
+        <v>46446</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="n"/>
@@ -74348,14 +74256,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G107" s="8" t="n">
-        <v>46783</v>
-      </c>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
       <c r="H107" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I107" s="7" t="n"/>
       <c r="J107" s="7" t="n"/>
@@ -74393,7 +74297,7 @@
         <v>46752</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="I108" s="7" t="n"/>
       <c r="J108" s="7" t="n"/>
@@ -74425,13 +74329,13 @@
         </is>
       </c>
       <c r="F109" s="8" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="G109" s="8" t="n">
-        <v>46752</v>
+        <v>46783</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I109" s="7" t="n"/>
       <c r="J109" s="7" t="n"/>
@@ -74462,14 +74366,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G110" s="8" t="n">
-        <v>46721</v>
-      </c>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="8" t="n"/>
       <c r="H110" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I110" s="7" t="n"/>
       <c r="J110" s="7" t="n"/>
@@ -74501,13 +74401,13 @@
         </is>
       </c>
       <c r="F111" s="8" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="G111" s="8" t="n">
-        <v>46752</v>
+        <v>46721</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="I111" s="7" t="n"/>
       <c r="J111" s="7" t="n"/>
@@ -74539,10 +74439,10 @@
         </is>
       </c>
       <c r="F112" s="8" t="n">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>46873</v>
+        <v>46843</v>
       </c>
       <c r="H112" s="7" t="n">
         <v>0.15</v>
@@ -74576,14 +74476,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G113" s="8" t="n">
-        <v>46904</v>
-      </c>
+      <c r="F113" s="8" t="n"/>
+      <c r="G113" s="8" t="n"/>
       <c r="H113" s="7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I113" s="7" t="n"/>
       <c r="J113" s="7" t="n"/>
@@ -74615,13 +74511,13 @@
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>46873</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I114" s="7" t="n"/>
       <c r="J114" s="7" t="n"/>
@@ -74653,7 +74549,7 @@
         </is>
       </c>
       <c r="F115" s="8" t="n">
-        <v>46388</v>
+        <v>46357</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>46873</v>
@@ -74690,14 +74586,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F116" s="8" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G116" s="8" t="n">
-        <v>46843</v>
-      </c>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="8" t="n"/>
       <c r="H116" s="7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="I116" s="7" t="n"/>
       <c r="J116" s="7" t="n"/>
@@ -74729,13 +74621,13 @@
         </is>
       </c>
       <c r="F117" s="8" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="G117" s="8" t="n">
         <v>46904</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I117" s="7" t="n"/>
       <c r="J117" s="7" t="n"/>
@@ -74773,7 +74665,7 @@
         <v>46904</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
@@ -74804,14 +74696,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G119" s="8" t="n">
-        <v>46904</v>
-      </c>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="8" t="n"/>
       <c r="H119" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I119" s="7" t="n"/>
       <c r="J119" s="7" t="n"/>
@@ -74846,10 +74734,10 @@
         <v>46023</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>46843</v>
+        <v>46873</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="n"/>
@@ -74881,13 +74769,13 @@
         </is>
       </c>
       <c r="F121" s="8" t="n">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>46843</v>
+        <v>46904</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I121" s="7" t="n"/>
       <c r="J121" s="7" t="n"/>
@@ -74918,14 +74806,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F122" s="8" t="n">
-        <v>46661</v>
-      </c>
-      <c r="G122" s="8" t="n">
-        <v>47573</v>
-      </c>
+      <c r="F122" s="8" t="n"/>
+      <c r="G122" s="8" t="n"/>
       <c r="H122" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I122" s="7" t="n"/>
       <c r="J122" s="7" t="n"/>
@@ -74963,7 +74847,7 @@
         <v>47514</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I123" s="7" t="n"/>
       <c r="J123" s="7" t="n"/>
@@ -74995,13 +74879,13 @@
         </is>
       </c>
       <c r="F124" s="8" t="n">
-        <v>46661</v>
+        <v>46692</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>47573</v>
+        <v>47542</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I124" s="7" t="n"/>
       <c r="J124" s="7" t="n"/>
@@ -75032,14 +74916,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n">
-        <v>46661</v>
-      </c>
-      <c r="G125" s="8" t="n">
-        <v>47573</v>
-      </c>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
       <c r="H125" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I125" s="7" t="n"/>
       <c r="J125" s="7" t="n"/>
@@ -75074,10 +74954,10 @@
         <v>46661</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>47514</v>
+        <v>47573</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I126" s="7" t="n"/>
       <c r="J126" s="7" t="n"/>
@@ -75109,13 +74989,13 @@
         </is>
       </c>
       <c r="F127" s="8" t="n">
-        <v>46508</v>
+        <v>46478</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>47480</v>
+        <v>47511</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I127" s="7" t="n"/>
       <c r="J127" s="7" t="n"/>
@@ -75146,14 +75026,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F128" s="8" t="n">
-        <v>46508</v>
-      </c>
-      <c r="G128" s="8" t="n">
-        <v>47480</v>
-      </c>
+      <c r="F128" s="8" t="n"/>
+      <c r="G128" s="8" t="n"/>
       <c r="H128" s="7" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="I128" s="7" t="n"/>
       <c r="J128" s="7" t="n"/>
@@ -75185,13 +75061,13 @@
         </is>
       </c>
       <c r="F129" s="8" t="n">
-        <v>46508</v>
+        <v>46478</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>47480</v>
+        <v>47542</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I129" s="7" t="n"/>
       <c r="J129" s="7" t="n"/>
@@ -75223,13 +75099,13 @@
         </is>
       </c>
       <c r="F130" s="8" t="n">
-        <v>46508</v>
+        <v>46447</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>47511</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="I130" s="7" t="n"/>
       <c r="J130" s="7" t="n"/>
@@ -75260,14 +75136,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F131" s="8" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G131" s="8" t="n">
-        <v>47480</v>
-      </c>
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="8" t="n"/>
       <c r="H131" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I131" s="7" t="n"/>
       <c r="J131" s="7" t="n"/>
@@ -75299,13 +75171,13 @@
         </is>
       </c>
       <c r="F132" s="8" t="n">
-        <v>46569</v>
+        <v>46600</v>
       </c>
       <c r="G132" s="8" t="n">
         <v>47483</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
@@ -75343,7 +75215,7 @@
         <v>47452</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I133" s="7" t="n"/>
       <c r="J133" s="7" t="n"/>
@@ -75374,14 +75246,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n">
-        <v>46631</v>
-      </c>
-      <c r="G134" s="8" t="n">
-        <v>47422</v>
-      </c>
+      <c r="F134" s="8" t="n"/>
+      <c r="G134" s="8" t="n"/>
       <c r="H134" s="7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="I134" s="7" t="n"/>
       <c r="J134" s="7" t="n"/>
@@ -75413,13 +75281,13 @@
         </is>
       </c>
       <c r="F135" s="8" t="n">
-        <v>46631</v>
+        <v>46600</v>
       </c>
       <c r="G135" s="8" t="n">
-        <v>47422</v>
+        <v>47452</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I135" s="7" t="n"/>
       <c r="J135" s="7" t="n"/>
@@ -75457,7 +75325,7 @@
         <v>47452</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I136" s="7" t="n"/>
       <c r="J136" s="7" t="n"/>
@@ -75488,14 +75356,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G137" s="8" t="n">
-        <v>47208</v>
-      </c>
+      <c r="F137" s="8" t="n"/>
+      <c r="G137" s="8" t="n"/>
       <c r="H137" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I137" s="7" t="n"/>
       <c r="J137" s="7" t="n"/>
@@ -75527,13 +75391,13 @@
         </is>
       </c>
       <c r="F138" s="8" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="G138" s="8" t="n">
-        <v>47208</v>
+        <v>47238</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="I138" s="7" t="n"/>
       <c r="J138" s="7" t="n"/>
@@ -75565,13 +75429,13 @@
         </is>
       </c>
       <c r="F139" s="8" t="n">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>47238</v>
+        <v>47208</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I139" s="7" t="n"/>
       <c r="J139" s="7" t="n"/>
@@ -75602,14 +75466,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G140" s="8" t="n">
-        <v>47269</v>
-      </c>
+      <c r="F140" s="8" t="n"/>
+      <c r="G140" s="8" t="n"/>
       <c r="H140" s="7" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="I140" s="7" t="n"/>
       <c r="J140" s="7" t="n"/>
@@ -75641,10 +75501,10 @@
         </is>
       </c>
       <c r="F141" s="8" t="n">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="G141" s="8" t="n">
-        <v>47269</v>
+        <v>47208</v>
       </c>
       <c r="H141" s="7" t="n">
         <v>0.17</v>
@@ -75679,13 +75539,13 @@
         </is>
       </c>
       <c r="F142" s="8" t="n">
-        <v>46631</v>
+        <v>46569</v>
       </c>
       <c r="G142" s="8" t="n">
-        <v>47633</v>
+        <v>47603</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I142" s="7" t="n"/>
       <c r="J142" s="7" t="n"/>
@@ -75716,14 +75576,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n">
-        <v>46631</v>
-      </c>
-      <c r="G143" s="8" t="n">
-        <v>47664</v>
-      </c>
+      <c r="F143" s="8" t="n"/>
+      <c r="G143" s="8" t="n"/>
       <c r="H143" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I143" s="7" t="n"/>
       <c r="J143" s="7" t="n"/>
@@ -75761,7 +75617,7 @@
         <v>47633</v>
       </c>
       <c r="H144" s="7" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="I144" s="7" t="n"/>
       <c r="J144" s="7" t="n"/>
@@ -75793,13 +75649,13 @@
         </is>
       </c>
       <c r="F145" s="8" t="n">
-        <v>46631</v>
+        <v>46600</v>
       </c>
       <c r="G145" s="8" t="n">
-        <v>47664</v>
+        <v>47633</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I145" s="7" t="n"/>
       <c r="J145" s="7" t="n"/>
@@ -75830,14 +75686,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n">
-        <v>46600</v>
-      </c>
-      <c r="G146" s="8" t="n">
-        <v>47603</v>
-      </c>
+      <c r="F146" s="8" t="n"/>
+      <c r="G146" s="8" t="n"/>
       <c r="H146" s="7" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="I146" s="7" t="n"/>
       <c r="J146" s="7" t="n"/>
@@ -75869,13 +75721,13 @@
         </is>
       </c>
       <c r="F147" s="8" t="n">
-        <v>45901</v>
+        <v>45962</v>
       </c>
       <c r="G147" s="8" t="n">
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I147" s="7" t="n"/>
       <c r="J147" s="7" t="n"/>
@@ -75913,7 +75765,7 @@
         <v>46630</v>
       </c>
       <c r="H148" s="7" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I148" s="7" t="n"/>
       <c r="J148" s="7" t="n"/>
@@ -75944,14 +75796,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n">
-        <v>45901</v>
-      </c>
-      <c r="G149" s="8" t="n">
-        <v>46630</v>
-      </c>
+      <c r="F149" s="8" t="n"/>
+      <c r="G149" s="8" t="n"/>
       <c r="H149" s="7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
@@ -75983,13 +75831,13 @@
         </is>
       </c>
       <c r="F150" s="8" t="n">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="G150" s="8" t="n">
-        <v>46568</v>
+        <v>46630</v>
       </c>
       <c r="H150" s="7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I150" s="7" t="n"/>
       <c r="J150" s="7" t="n"/>
@@ -76024,10 +75872,10 @@
         <v>45931</v>
       </c>
       <c r="G151" s="8" t="n">
-        <v>46630</v>
+        <v>46568</v>
       </c>
       <c r="H151" s="7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I151" s="7" t="n"/>
       <c r="J151" s="7" t="n"/>
@@ -76058,14 +75906,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F152" s="8" t="n">
-        <v>46539</v>
-      </c>
-      <c r="G152" s="8" t="n">
-        <v>47208</v>
-      </c>
+      <c r="F152" s="8" t="n"/>
+      <c r="G152" s="8" t="n"/>
       <c r="H152" s="7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I152" s="7" t="n"/>
       <c r="J152" s="7" t="n"/>
@@ -76097,13 +75941,13 @@
         </is>
       </c>
       <c r="F153" s="8" t="n">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="G153" s="8" t="n">
-        <v>47177</v>
+        <v>47208</v>
       </c>
       <c r="H153" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I153" s="7" t="n"/>
       <c r="J153" s="7" t="n"/>
@@ -76141,7 +75985,7 @@
         <v>47177</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I154" s="7" t="n"/>
       <c r="J154" s="7" t="n"/>
@@ -76172,14 +76016,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F155" s="8" t="n">
-        <v>46508</v>
-      </c>
-      <c r="G155" s="8" t="n">
-        <v>47177</v>
-      </c>
+      <c r="F155" s="8" t="n"/>
+      <c r="G155" s="8" t="n"/>
       <c r="H155" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I155" s="7" t="n"/>
       <c r="J155" s="7" t="n"/>
@@ -76211,10 +76051,10 @@
         </is>
       </c>
       <c r="F156" s="8" t="n">
-        <v>46508</v>
+        <v>46478</v>
       </c>
       <c r="G156" s="8" t="n">
-        <v>47177</v>
+        <v>47208</v>
       </c>
       <c r="H156" s="7" t="n">
         <v>0.15</v>
@@ -76252,7 +76092,7 @@
         <v>46874</v>
       </c>
       <c r="G157" s="8" t="n">
-        <v>47391</v>
+        <v>47422</v>
       </c>
       <c r="H157" s="7" t="n">
         <v>0.15</v>
@@ -76286,14 +76126,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F158" s="8" t="n">
-        <v>46905</v>
-      </c>
-      <c r="G158" s="8" t="n">
-        <v>47361</v>
-      </c>
+      <c r="F158" s="8" t="n"/>
+      <c r="G158" s="8" t="n"/>
       <c r="H158" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I158" s="7" t="n"/>
       <c r="J158" s="7" t="n"/>
@@ -76325,13 +76161,13 @@
         </is>
       </c>
       <c r="F159" s="8" t="n">
-        <v>46874</v>
+        <v>46935</v>
       </c>
       <c r="G159" s="8" t="n">
         <v>47361</v>
       </c>
       <c r="H159" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I159" s="7" t="n"/>
       <c r="J159" s="7" t="n"/>
@@ -76363,13 +76199,13 @@
         </is>
       </c>
       <c r="F160" s="8" t="n">
-        <v>46905</v>
+        <v>46935</v>
       </c>
       <c r="G160" s="8" t="n">
         <v>47361</v>
       </c>
       <c r="H160" s="7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="I160" s="7" t="n"/>
       <c r="J160" s="7" t="n"/>
@@ -76400,14 +76236,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
-        <v>46874</v>
-      </c>
-      <c r="G161" s="8" t="n">
-        <v>47422</v>
-      </c>
+      <c r="F161" s="8" t="n"/>
+      <c r="G161" s="8" t="n"/>
       <c r="H161" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I161" s="7" t="n"/>
       <c r="J161" s="7" t="n"/>
@@ -76439,13 +76271,13 @@
         </is>
       </c>
       <c r="F162" s="8" t="n">
-        <v>46419</v>
+        <v>46478</v>
       </c>
       <c r="G162" s="8" t="n">
-        <v>46934</v>
+        <v>46904</v>
       </c>
       <c r="H162" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I162" s="7" t="n"/>
       <c r="J162" s="7" t="n"/>
@@ -76477,13 +76309,13 @@
         </is>
       </c>
       <c r="F163" s="8" t="n">
-        <v>46419</v>
+        <v>46478</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>46965</v>
+        <v>46934</v>
       </c>
       <c r="H163" s="7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="I163" s="7" t="n"/>
       <c r="J163" s="7" t="n"/>
@@ -76514,14 +76346,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G164" s="8" t="n">
-        <v>46965</v>
-      </c>
+      <c r="F164" s="8" t="n"/>
+      <c r="G164" s="8" t="n"/>
       <c r="H164" s="7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I164" s="7" t="n"/>
       <c r="J164" s="7" t="n"/>
@@ -76553,13 +76381,13 @@
         </is>
       </c>
       <c r="F165" s="8" t="n">
-        <v>46419</v>
+        <v>46478</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>46904</v>
+        <v>46965</v>
       </c>
       <c r="H165" s="7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="I165" s="7" t="n"/>
       <c r="J165" s="7" t="n"/>
@@ -76628,14 +76456,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F167" s="8" t="n">
-        <v>46661</v>
-      </c>
-      <c r="G167" s="8" t="n">
-        <v>47694</v>
-      </c>
+      <c r="F167" s="8" t="n"/>
+      <c r="G167" s="8" t="n"/>
       <c r="H167" s="7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I167" s="7" t="n"/>
       <c r="J167" s="7" t="n"/>
@@ -76667,10 +76491,10 @@
         </is>
       </c>
       <c r="F168" s="8" t="n">
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="G168" s="8" t="n">
-        <v>47756</v>
+        <v>47694</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>0.15</v>
@@ -76705,13 +76529,13 @@
         </is>
       </c>
       <c r="F169" s="8" t="n">
-        <v>46692</v>
+        <v>46722</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>47725</v>
+        <v>47694</v>
       </c>
       <c r="H169" s="7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="I169" s="7" t="n"/>
       <c r="J169" s="7" t="n"/>
@@ -76742,14 +76566,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F170" s="8" t="n">
-        <v>46661</v>
-      </c>
-      <c r="G170" s="8" t="n">
-        <v>47756</v>
-      </c>
+      <c r="F170" s="8" t="n"/>
+      <c r="G170" s="8" t="n"/>
       <c r="H170" s="7" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I170" s="7" t="n"/>
       <c r="J170" s="7" t="n"/>
@@ -76787,7 +76607,7 @@
         <v>47756</v>
       </c>
       <c r="H171" s="7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I171" s="7" t="n"/>
       <c r="J171" s="7" t="n"/>
@@ -76819,13 +76639,13 @@
         </is>
       </c>
       <c r="F172" s="8" t="n">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="G172" s="8" t="n">
-        <v>46903</v>
+        <v>46934</v>
       </c>
       <c r="H172" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I172" s="7" t="n"/>
       <c r="J172" s="7" t="n"/>
@@ -76856,14 +76676,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F173" s="8" t="n">
-        <v>45658</v>
-      </c>
-      <c r="G173" s="8" t="n">
-        <v>46934</v>
-      </c>
+      <c r="F173" s="8" t="n"/>
+      <c r="G173" s="8" t="n"/>
       <c r="H173" s="7" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="I173" s="7" t="n"/>
       <c r="J173" s="7" t="n"/>
@@ -76895,13 +76711,13 @@
         </is>
       </c>
       <c r="F174" s="8" t="n">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="G174" s="8" t="n">
-        <v>46873</v>
+        <v>46903</v>
       </c>
       <c r="H174" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I174" s="7" t="n"/>
       <c r="J174" s="7" t="n"/>
@@ -76933,13 +76749,13 @@
         </is>
       </c>
       <c r="F175" s="8" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="G175" s="8" t="n">
-        <v>46873</v>
+        <v>46934</v>
       </c>
       <c r="H175" s="7" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I175" s="7" t="n"/>
       <c r="J175" s="7" t="n"/>
@@ -76970,14 +76786,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F176" s="8" t="n">
-        <v>45658</v>
-      </c>
-      <c r="G176" s="8" t="n">
-        <v>46903</v>
-      </c>
+      <c r="F176" s="8" t="n"/>
+      <c r="G176" s="8" t="n"/>
       <c r="H176" s="7" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="I176" s="7" t="n"/>
       <c r="J176" s="7" t="n"/>
@@ -77009,13 +76821,13 @@
         </is>
       </c>
       <c r="F177" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>46843</v>
       </c>
       <c r="H177" s="7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="I177" s="7" t="n"/>
       <c r="J177" s="7" t="n"/>
@@ -77047,13 +76859,13 @@
         </is>
       </c>
       <c r="F178" s="8" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="G178" s="8" t="n">
         <v>46783</v>
       </c>
       <c r="H178" s="7" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I178" s="7" t="n"/>
       <c r="J178" s="7" t="n"/>
@@ -77084,14 +76896,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F179" s="8" t="n">
-        <v>45962</v>
-      </c>
-      <c r="G179" s="8" t="n">
-        <v>46812</v>
-      </c>
+      <c r="F179" s="8" t="n"/>
+      <c r="G179" s="8" t="n"/>
       <c r="H179" s="7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I179" s="7" t="n"/>
       <c r="J179" s="7" t="n"/>
@@ -77123,13 +76931,13 @@
         </is>
       </c>
       <c r="F180" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G180" s="8" t="n">
         <v>46783</v>
       </c>
       <c r="H180" s="7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I180" s="7" t="n"/>
       <c r="J180" s="7" t="n"/>
@@ -77161,13 +76969,13 @@
         </is>
       </c>
       <c r="F181" s="8" t="n">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="G181" s="8" t="n">
-        <v>46783</v>
+        <v>46843</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I181" s="7" t="n"/>
       <c r="J181" s="7" t="n"/>
@@ -77198,14 +77006,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F182" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G182" s="8" t="n">
-        <v>46965</v>
-      </c>
+      <c r="F182" s="8" t="n"/>
+      <c r="G182" s="8" t="n"/>
       <c r="H182" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I182" s="7" t="n"/>
       <c r="J182" s="7" t="n"/>
@@ -77237,13 +77041,13 @@
         </is>
       </c>
       <c r="F183" s="8" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="G183" s="8" t="n">
         <v>46965</v>
       </c>
       <c r="H183" s="7" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I183" s="7" t="n"/>
       <c r="J183" s="7" t="n"/>
@@ -77278,10 +77082,10 @@
         <v>46082</v>
       </c>
       <c r="G184" s="8" t="n">
-        <v>46934</v>
+        <v>46904</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I184" s="7" t="n"/>
       <c r="J184" s="7" t="n"/>
@@ -77312,14 +77116,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F185" s="8" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G185" s="8" t="n">
-        <v>46934</v>
-      </c>
+      <c r="F185" s="8" t="n"/>
+      <c r="G185" s="8" t="n"/>
       <c r="H185" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I185" s="7" t="n"/>
       <c r="J185" s="7" t="n"/>
@@ -77354,10 +77154,10 @@
         <v>46113</v>
       </c>
       <c r="G186" s="8" t="n">
-        <v>46904</v>
+        <v>46965</v>
       </c>
       <c r="H186" s="7" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="I186" s="7" t="n"/>
       <c r="J186" s="7" t="n"/>
@@ -77426,14 +77226,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F188" s="8" t="n">
-        <v>45962</v>
-      </c>
-      <c r="G188" s="8" t="n">
-        <v>46996</v>
-      </c>
+      <c r="F188" s="8" t="n"/>
+      <c r="G188" s="8" t="n"/>
       <c r="H188" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I188" s="7" t="n"/>
       <c r="J188" s="7" t="n"/>
@@ -77468,10 +77264,10 @@
         <v>46023</v>
       </c>
       <c r="G189" s="8" t="n">
-        <v>47026</v>
+        <v>46996</v>
       </c>
       <c r="H189" s="7" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I189" s="7" t="n"/>
       <c r="J189" s="7" t="n"/>
@@ -77506,10 +77302,10 @@
         <v>45962</v>
       </c>
       <c r="G190" s="8" t="n">
-        <v>46996</v>
+        <v>47026</v>
       </c>
       <c r="H190" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I190" s="7" t="n"/>
       <c r="J190" s="7" t="n"/>
@@ -77540,14 +77336,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F191" s="8" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G191" s="8" t="n">
-        <v>47057</v>
-      </c>
+      <c r="F191" s="8" t="n"/>
+      <c r="G191" s="8" t="n"/>
       <c r="H191" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I191" s="7" t="n"/>
       <c r="J191" s="7" t="n"/>
@@ -77579,13 +77371,13 @@
         </is>
       </c>
       <c r="F192" s="8" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G192" s="8" t="n">
         <v>47542</v>
       </c>
       <c r="H192" s="7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I192" s="7" t="n"/>
       <c r="J192" s="7" t="n"/>
@@ -77617,13 +77409,13 @@
         </is>
       </c>
       <c r="F193" s="8" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>47480</v>
+        <v>47542</v>
       </c>
       <c r="H193" s="7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I193" s="7" t="n"/>
       <c r="J193" s="7" t="n"/>
@@ -77654,14 +77446,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F194" s="8" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G194" s="8" t="n">
-        <v>47542</v>
-      </c>
+      <c r="F194" s="8" t="n"/>
+      <c r="G194" s="8" t="n"/>
       <c r="H194" s="7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="I194" s="7" t="n"/>
       <c r="J194" s="7" t="n"/>
@@ -77693,13 +77481,13 @@
         </is>
       </c>
       <c r="F195" s="8" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="G195" s="8" t="n">
         <v>47511</v>
       </c>
       <c r="H195" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I195" s="7" t="n"/>
       <c r="J195" s="7" t="n"/>
@@ -77731,13 +77519,13 @@
         </is>
       </c>
       <c r="F196" s="8" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="G196" s="8" t="n">
-        <v>47480</v>
+        <v>47511</v>
       </c>
       <c r="H196" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I196" s="7" t="n"/>
       <c r="J196" s="7" t="n"/>
@@ -77768,14 +77556,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F197" s="8" t="n">
-        <v>45901</v>
-      </c>
-      <c r="G197" s="8" t="n">
-        <v>46418</v>
-      </c>
+      <c r="F197" s="8" t="n"/>
+      <c r="G197" s="8" t="n"/>
       <c r="H197" s="7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I197" s="7" t="n"/>
       <c r="J197" s="7" t="n"/>
@@ -77813,7 +77597,7 @@
         <v>46387</v>
       </c>
       <c r="H198" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I198" s="7" t="n"/>
       <c r="J198" s="7" t="n"/>
@@ -77845,13 +77629,13 @@
         </is>
       </c>
       <c r="F199" s="8" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="G199" s="8" t="n">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="H199" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I199" s="7" t="n"/>
       <c r="J199" s="7" t="n"/>
@@ -77882,14 +77666,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F200" s="8" t="n">
-        <v>45901</v>
-      </c>
-      <c r="G200" s="8" t="n">
-        <v>46387</v>
-      </c>
+      <c r="F200" s="8" t="n"/>
+      <c r="G200" s="8" t="n"/>
       <c r="H200" s="7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I200" s="7" t="n"/>
       <c r="J200" s="7" t="n"/>
@@ -77921,13 +77701,13 @@
         </is>
       </c>
       <c r="F201" s="8" t="n">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="G201" s="8" t="n">
-        <v>46418</v>
+        <v>46356</v>
       </c>
       <c r="H201" s="7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="I201" s="7" t="n"/>
       <c r="J201" s="7" t="n"/>
@@ -77962,10 +77742,10 @@
         <v>46419</v>
       </c>
       <c r="G202" s="8" t="n">
-        <v>47633</v>
+        <v>47664</v>
       </c>
       <c r="H202" s="7" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="I202" s="7" t="n"/>
       <c r="J202" s="7" t="n"/>
@@ -77996,14 +77776,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F203" s="8" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G203" s="8" t="n">
-        <v>47664</v>
-      </c>
+      <c r="F203" s="8" t="n"/>
+      <c r="G203" s="8" t="n"/>
       <c r="H203" s="7" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="I203" s="7" t="n"/>
       <c r="J203" s="7" t="n"/>
@@ -78038,10 +77814,10 @@
         <v>46419</v>
       </c>
       <c r="G204" s="8" t="n">
-        <v>47603</v>
+        <v>47633</v>
       </c>
       <c r="H204" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I204" s="7" t="n"/>
       <c r="J204" s="7" t="n"/>
@@ -78076,7 +77852,7 @@
         <v>46447</v>
       </c>
       <c r="G205" s="8" t="n">
-        <v>47603</v>
+        <v>47633</v>
       </c>
       <c r="H205" s="7" t="n">
         <v>0.11</v>
@@ -78110,12 +77886,8 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F206" s="8" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G206" s="8" t="n">
-        <v>47664</v>
-      </c>
+      <c r="F206" s="8" t="n"/>
+      <c r="G206" s="8" t="n"/>
       <c r="H206" s="7" t="n">
         <v>0.15</v>
       </c>
@@ -78155,7 +77927,7 @@
         <v>47329</v>
       </c>
       <c r="H207" s="7" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="I207" s="7" t="n"/>
       <c r="J207" s="7" t="n"/>
@@ -78190,10 +77962,10 @@
         <v>46478</v>
       </c>
       <c r="G208" s="8" t="n">
-        <v>47360</v>
+        <v>47329</v>
       </c>
       <c r="H208" s="7" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I208" s="7" t="n"/>
       <c r="J208" s="7" t="n"/>
@@ -78224,12 +77996,8 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F209" s="8" t="n">
-        <v>46508</v>
-      </c>
-      <c r="G209" s="8" t="n">
-        <v>47329</v>
-      </c>
+      <c r="F209" s="8" t="n"/>
+      <c r="G209" s="8" t="n"/>
       <c r="H209" s="7" t="n">
         <v>0.11</v>
       </c>
@@ -78266,7 +78034,7 @@
         <v>46478</v>
       </c>
       <c r="G210" s="8" t="n">
-        <v>47360</v>
+        <v>47329</v>
       </c>
       <c r="H210" s="7" t="n">
         <v>0.13</v>
@@ -78301,13 +78069,13 @@
         </is>
       </c>
       <c r="F211" s="8" t="n">
-        <v>46508</v>
+        <v>46478</v>
       </c>
       <c r="G211" s="8" t="n">
-        <v>47391</v>
+        <v>47329</v>
       </c>
       <c r="H211" s="7" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I211" s="7" t="n"/>
       <c r="J211" s="7" t="n"/>
@@ -78338,14 +78106,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F212" s="8" t="n">
-        <v>46600</v>
-      </c>
-      <c r="G212" s="8" t="n">
-        <v>47664</v>
-      </c>
+      <c r="F212" s="8" t="n"/>
+      <c r="G212" s="8" t="n"/>
       <c r="H212" s="7" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I212" s="7" t="n"/>
       <c r="J212" s="7" t="n"/>
@@ -78383,7 +78147,7 @@
         <v>47633</v>
       </c>
       <c r="H213" s="7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="I213" s="7" t="n"/>
       <c r="J213" s="7" t="n"/>
@@ -78415,10 +78179,10 @@
         </is>
       </c>
       <c r="F214" s="8" t="n">
-        <v>46569</v>
+        <v>46600</v>
       </c>
       <c r="G214" s="8" t="n">
-        <v>47664</v>
+        <v>47603</v>
       </c>
       <c r="H214" s="7" t="n">
         <v>0.12</v>
@@ -78452,14 +78216,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F215" s="8" t="n">
-        <v>46569</v>
-      </c>
-      <c r="G215" s="8" t="n">
-        <v>47664</v>
-      </c>
+      <c r="F215" s="8" t="n"/>
+      <c r="G215" s="8" t="n"/>
       <c r="H215" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I215" s="7" t="n"/>
       <c r="J215" s="7" t="n"/>
@@ -78491,10 +78251,10 @@
         </is>
       </c>
       <c r="F216" s="8" t="n">
-        <v>46600</v>
+        <v>46569</v>
       </c>
       <c r="G216" s="8" t="n">
-        <v>47664</v>
+        <v>47603</v>
       </c>
       <c r="H216" s="7" t="n">
         <v>0.11</v>
@@ -78535,7 +78295,7 @@
         <v>46538</v>
       </c>
       <c r="H217" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I217" s="7" t="n"/>
       <c r="J217" s="7" t="n"/>
@@ -78566,14 +78326,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F218" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G218" s="8" t="n">
-        <v>46507</v>
-      </c>
+      <c r="F218" s="8" t="n"/>
+      <c r="G218" s="8" t="n"/>
       <c r="H218" s="7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="I218" s="7" t="n"/>
       <c r="J218" s="7" t="n"/>
@@ -78605,10 +78361,10 @@
         </is>
       </c>
       <c r="F219" s="8" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="G219" s="8" t="n">
-        <v>46507</v>
+        <v>46538</v>
       </c>
       <c r="H219" s="7" t="n">
         <v>0.11</v>
@@ -78643,13 +78399,13 @@
         </is>
       </c>
       <c r="F220" s="8" t="n">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="G220" s="8" t="n">
         <v>46507</v>
       </c>
       <c r="H220" s="7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I220" s="7" t="n"/>
       <c r="J220" s="7" t="n"/>
@@ -78680,14 +78436,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F221" s="8" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G221" s="8" t="n">
-        <v>46507</v>
-      </c>
+      <c r="F221" s="8" t="n"/>
+      <c r="G221" s="8" t="n"/>
       <c r="H221" s="7" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I221" s="7" t="n"/>
       <c r="J221" s="7" t="n"/>
@@ -78719,13 +78471,13 @@
         </is>
       </c>
       <c r="F222" s="8" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="G222" s="8" t="n">
         <v>46630</v>
       </c>
       <c r="H222" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I222" s="7" t="n"/>
       <c r="J222" s="7" t="n"/>
@@ -78794,12 +78546,8 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F224" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G224" s="8" t="n">
-        <v>46568</v>
-      </c>
+      <c r="F224" s="8" t="n"/>
+      <c r="G224" s="8" t="n"/>
       <c r="H224" s="7" t="n">
         <v>0.14</v>
       </c>
@@ -78833,13 +78581,13 @@
         </is>
       </c>
       <c r="F225" s="8" t="n">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="G225" s="8" t="n">
         <v>46568</v>
       </c>
       <c r="H225" s="7" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I225" s="7" t="n"/>
       <c r="J225" s="7" t="n"/>
@@ -78871,13 +78619,13 @@
         </is>
       </c>
       <c r="F226" s="8" t="n">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="G226" s="8" t="n">
-        <v>46568</v>
+        <v>46630</v>
       </c>
       <c r="H226" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I226" s="7" t="n"/>
       <c r="J226" s="7" t="n"/>
@@ -78908,12 +78656,8 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F227" s="8" t="n">
-        <v>46174</v>
-      </c>
-      <c r="G227" s="8" t="n">
-        <v>46996</v>
-      </c>
+      <c r="F227" s="8" t="n"/>
+      <c r="G227" s="8" t="n"/>
       <c r="H227" s="7" t="n">
         <v>0.12</v>
       </c>
@@ -78947,13 +78691,13 @@
         </is>
       </c>
       <c r="F228" s="8" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="G228" s="8" t="n">
-        <v>46996</v>
+        <v>47026</v>
       </c>
       <c r="H228" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I228" s="7" t="n"/>
       <c r="J228" s="7" t="n"/>
@@ -78985,13 +78729,13 @@
         </is>
       </c>
       <c r="F229" s="8" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="G229" s="8" t="n">
-        <v>46996</v>
+        <v>47026</v>
       </c>
       <c r="H229" s="7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I229" s="7" t="n"/>
       <c r="J229" s="7" t="n"/>
@@ -79022,14 +78766,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F230" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="G230" s="8" t="n">
-        <v>46996</v>
-      </c>
+      <c r="F230" s="8" t="n"/>
+      <c r="G230" s="8" t="n"/>
       <c r="H230" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I230" s="7" t="n"/>
       <c r="J230" s="7" t="n"/>
@@ -79067,7 +78807,7 @@
         <v>46996</v>
       </c>
       <c r="H231" s="7" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="I231" s="7" t="n"/>
       <c r="J231" s="7" t="n"/>
@@ -79099,13 +78839,13 @@
         </is>
       </c>
       <c r="F232" s="8" t="n">
-        <v>46419</v>
+        <v>46357</v>
       </c>
       <c r="G232" s="8" t="n">
         <v>47391</v>
       </c>
       <c r="H232" s="7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I232" s="7" t="n"/>
       <c r="J232" s="7" t="n"/>
@@ -79136,14 +78876,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F233" s="8" t="n">
-        <v>46357</v>
-      </c>
-      <c r="G233" s="8" t="n">
-        <v>47391</v>
-      </c>
+      <c r="F233" s="8" t="n"/>
+      <c r="G233" s="8" t="n"/>
       <c r="H233" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I233" s="7" t="n"/>
       <c r="J233" s="7" t="n"/>
@@ -79175,13 +78911,13 @@
         </is>
       </c>
       <c r="F234" s="8" t="n">
-        <v>46357</v>
+        <v>46388</v>
       </c>
       <c r="G234" s="8" t="n">
-        <v>47391</v>
+        <v>47421</v>
       </c>
       <c r="H234" s="7" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I234" s="7" t="n"/>
       <c r="J234" s="7" t="n"/>
@@ -79213,13 +78949,13 @@
         </is>
       </c>
       <c r="F235" s="8" t="n">
-        <v>46388</v>
+        <v>46419</v>
       </c>
       <c r="G235" s="8" t="n">
-        <v>47391</v>
+        <v>47421</v>
       </c>
       <c r="H235" s="7" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="I235" s="7" t="n"/>
       <c r="J235" s="7" t="n"/>
@@ -79250,12 +78986,8 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F236" s="8" t="n">
-        <v>46388</v>
-      </c>
-      <c r="G236" s="8" t="n">
-        <v>47452</v>
-      </c>
+      <c r="F236" s="8" t="n"/>
+      <c r="G236" s="8" t="n"/>
       <c r="H236" s="7" t="n">
         <v>0.14</v>
       </c>
@@ -79292,10 +79024,10 @@
         <v>46661</v>
       </c>
       <c r="G237" s="8" t="n">
-        <v>47725</v>
+        <v>47756</v>
       </c>
       <c r="H237" s="7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I237" s="7" t="n"/>
       <c r="J237" s="7" t="n"/>
@@ -79327,13 +79059,13 @@
         </is>
       </c>
       <c r="F238" s="8" t="n">
-        <v>46692</v>
+        <v>46661</v>
       </c>
       <c r="G238" s="8" t="n">
-        <v>47694</v>
+        <v>47725</v>
       </c>
       <c r="H238" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I238" s="7" t="n"/>
       <c r="J238" s="7" t="n"/>
@@ -79364,14 +79096,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F239" s="8" t="n">
-        <v>46722</v>
-      </c>
-      <c r="G239" s="8" t="n">
-        <v>47694</v>
-      </c>
+      <c r="F239" s="8" t="n"/>
+      <c r="G239" s="8" t="n"/>
       <c r="H239" s="7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="I239" s="7" t="n"/>
       <c r="J239" s="7" t="n"/>
@@ -79403,13 +79131,13 @@
         </is>
       </c>
       <c r="F240" s="8" t="n">
-        <v>46722</v>
+        <v>46661</v>
       </c>
       <c r="G240" s="8" t="n">
-        <v>47725</v>
+        <v>47756</v>
       </c>
       <c r="H240" s="7" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I240" s="7" t="n"/>
       <c r="J240" s="7" t="n"/>
@@ -79441,13 +79169,13 @@
         </is>
       </c>
       <c r="F241" s="8" t="n">
-        <v>46722</v>
+        <v>46661</v>
       </c>
       <c r="G241" s="8" t="n">
         <v>47725</v>
       </c>
       <c r="H241" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I241" s="7" t="n"/>
       <c r="J241" s="7" t="n"/>
@@ -79478,14 +79206,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F242" s="8" t="n">
-        <v>46784</v>
-      </c>
-      <c r="G242" s="8" t="n">
-        <v>47391</v>
-      </c>
+      <c r="F242" s="8" t="n"/>
+      <c r="G242" s="8" t="n"/>
       <c r="H242" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I242" s="7" t="n"/>
       <c r="J242" s="7" t="n"/>
@@ -79517,13 +79241,13 @@
         </is>
       </c>
       <c r="F243" s="8" t="n">
-        <v>46753</v>
+        <v>46784</v>
       </c>
       <c r="G243" s="8" t="n">
-        <v>47452</v>
+        <v>47421</v>
       </c>
       <c r="H243" s="7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I243" s="7" t="n"/>
       <c r="J243" s="7" t="n"/>
@@ -79555,13 +79279,13 @@
         </is>
       </c>
       <c r="F244" s="8" t="n">
-        <v>46784</v>
+        <v>46722</v>
       </c>
       <c r="G244" s="8" t="n">
-        <v>47391</v>
+        <v>47452</v>
       </c>
       <c r="H244" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I244" s="7" t="n"/>
       <c r="J244" s="7" t="n"/>
@@ -79592,12 +79316,8 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F245" s="8" t="n">
-        <v>46722</v>
-      </c>
-      <c r="G245" s="8" t="n">
-        <v>47391</v>
-      </c>
+      <c r="F245" s="8" t="n"/>
+      <c r="G245" s="8" t="n"/>
       <c r="H245" s="7" t="n">
         <v>0.16</v>
       </c>
@@ -79631,13 +79351,13 @@
         </is>
       </c>
       <c r="F246" s="8" t="n">
-        <v>46722</v>
+        <v>46753</v>
       </c>
       <c r="G246" s="8" t="n">
-        <v>47391</v>
+        <v>47452</v>
       </c>
       <c r="H246" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I246" s="7" t="n"/>
       <c r="J246" s="7" t="n"/>
@@ -79669,13 +79389,13 @@
         </is>
       </c>
       <c r="F247" s="8" t="n">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="G247" s="8" t="n">
         <v>46599</v>
       </c>
       <c r="H247" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I247" s="7" t="n"/>
       <c r="J247" s="7" t="n"/>
@@ -79706,14 +79426,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F248" s="8" t="n">
-        <v>45748</v>
-      </c>
-      <c r="G248" s="8" t="n">
-        <v>46568</v>
-      </c>
+      <c r="F248" s="8" t="n"/>
+      <c r="G248" s="8" t="n"/>
       <c r="H248" s="7" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I248" s="7" t="n"/>
       <c r="J248" s="7" t="n"/>
@@ -79745,13 +79461,13 @@
         </is>
       </c>
       <c r="F249" s="8" t="n">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="G249" s="8" t="n">
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="H249" s="7" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="I249" s="7" t="n"/>
       <c r="J249" s="7" t="n"/>
@@ -79783,13 +79499,13 @@
         </is>
       </c>
       <c r="F250" s="8" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="G250" s="8" t="n">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="H250" s="7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I250" s="7" t="n"/>
       <c r="J250" s="7" t="n"/>
@@ -79820,14 +79536,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F251" s="8" t="n">
-        <v>45778</v>
-      </c>
-      <c r="G251" s="8" t="n">
-        <v>46568</v>
-      </c>
+      <c r="F251" s="8" t="n"/>
+      <c r="G251" s="8" t="n"/>
       <c r="H251" s="7" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I251" s="7" t="n"/>
       <c r="J251" s="7" t="n"/>
@@ -79859,13 +79571,13 @@
         </is>
       </c>
       <c r="F252" s="8" t="n">
-        <v>46692</v>
+        <v>46753</v>
       </c>
       <c r="G252" s="8" t="n">
         <v>47207</v>
       </c>
       <c r="H252" s="7" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="I252" s="7" t="n"/>
       <c r="J252" s="7" t="n"/>
@@ -79903,7 +79615,7 @@
         <v>47207</v>
       </c>
       <c r="H253" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I253" s="7" t="n"/>
       <c r="J253" s="7" t="n"/>
@@ -79934,14 +79646,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F254" s="8" t="n">
-        <v>46722</v>
-      </c>
-      <c r="G254" s="8" t="n">
-        <v>47177</v>
-      </c>
+      <c r="F254" s="8" t="n"/>
+      <c r="G254" s="8" t="n"/>
       <c r="H254" s="7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I254" s="7" t="n"/>
       <c r="J254" s="7" t="n"/>
@@ -79973,13 +79681,13 @@
         </is>
       </c>
       <c r="F255" s="8" t="n">
-        <v>46722</v>
+        <v>46753</v>
       </c>
       <c r="G255" s="8" t="n">
-        <v>46934</v>
+        <v>46996</v>
       </c>
       <c r="H255" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I255" s="7" t="n"/>
       <c r="J255" s="7" t="n"/>
@@ -80011,13 +79719,13 @@
         </is>
       </c>
       <c r="F256" s="8" t="n">
-        <v>46722</v>
+        <v>46753</v>
       </c>
       <c r="G256" s="8" t="n">
-        <v>46996</v>
+        <v>46934</v>
       </c>
       <c r="H256" s="7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="I256" s="7" t="n"/>
       <c r="J256" s="7" t="n"/>
@@ -80048,14 +79756,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F257" s="8" t="n">
-        <v>46753</v>
-      </c>
-      <c r="G257" s="8" t="n">
-        <v>46934</v>
-      </c>
+      <c r="F257" s="8" t="n"/>
+      <c r="G257" s="8" t="n"/>
       <c r="H257" s="7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I257" s="7" t="n"/>
       <c r="J257" s="7" t="n"/>
@@ -80087,13 +79791,13 @@
         </is>
       </c>
       <c r="F258" s="8" t="n">
-        <v>46447</v>
+        <v>46388</v>
       </c>
       <c r="G258" s="8" t="n">
-        <v>46752</v>
+        <v>46721</v>
       </c>
       <c r="H258" s="7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I258" s="7" t="n"/>
       <c r="J258" s="7" t="n"/>
@@ -80125,13 +79829,13 @@
         </is>
       </c>
       <c r="F259" s="8" t="n">
-        <v>46447</v>
+        <v>46388</v>
       </c>
       <c r="G259" s="8" t="n">
         <v>46752</v>
       </c>
       <c r="H259" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I259" s="7" t="n"/>
       <c r="J259" s="7" t="n"/>
@@ -80162,14 +79866,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F260" s="8" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G260" s="8" t="n">
-        <v>46721</v>
-      </c>
+      <c r="F260" s="8" t="n"/>
+      <c r="G260" s="8" t="n"/>
       <c r="H260" s="7" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I260" s="7" t="n"/>
       <c r="J260" s="7" t="n"/>
@@ -80204,10 +79904,10 @@
         <v>46478</v>
       </c>
       <c r="G261" s="8" t="n">
-        <v>46964</v>
+        <v>46995</v>
       </c>
       <c r="H261" s="7" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="I261" s="7" t="n"/>
       <c r="J261" s="7" t="n"/>
@@ -80239,13 +79939,13 @@
         </is>
       </c>
       <c r="F262" s="8" t="n">
-        <v>46539</v>
+        <v>46478</v>
       </c>
       <c r="G262" s="8" t="n">
-        <v>46964</v>
+        <v>47026</v>
       </c>
       <c r="H262" s="7" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="I262" s="7" t="n"/>
       <c r="J262" s="7" t="n"/>
@@ -80276,14 +79976,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F263" s="8" t="n">
-        <v>46508</v>
-      </c>
-      <c r="G263" s="8" t="n">
-        <v>47026</v>
-      </c>
+      <c r="F263" s="8" t="n"/>
+      <c r="G263" s="8" t="n"/>
       <c r="H263" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I263" s="7" t="n"/>
       <c r="J263" s="7" t="n"/>
@@ -80315,7 +80011,7 @@
         </is>
       </c>
       <c r="F264" s="8" t="n">
-        <v>46569</v>
+        <v>46508</v>
       </c>
       <c r="G264" s="8" t="n">
         <v>46752</v>
@@ -80353,13 +80049,13 @@
         </is>
       </c>
       <c r="F265" s="8" t="n">
-        <v>46539</v>
+        <v>46508</v>
       </c>
       <c r="G265" s="8" t="n">
-        <v>46783</v>
+        <v>46721</v>
       </c>
       <c r="H265" s="7" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="I265" s="7" t="n"/>
       <c r="J265" s="7" t="n"/>
@@ -80390,14 +80086,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F266" s="8" t="n">
-        <v>46539</v>
-      </c>
-      <c r="G266" s="8" t="n">
-        <v>46752</v>
-      </c>
+      <c r="F266" s="8" t="n"/>
+      <c r="G266" s="8" t="n"/>
       <c r="H266" s="7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I266" s="7" t="n"/>
       <c r="J266" s="7" t="n"/>
@@ -80429,13 +80121,13 @@
         </is>
       </c>
       <c r="F267" s="8" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="G267" s="8" t="n">
         <v>46418</v>
       </c>
       <c r="H267" s="7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I267" s="7" t="n"/>
       <c r="J267" s="7" t="n"/>
@@ -80473,7 +80165,7 @@
         <v>46477</v>
       </c>
       <c r="H268" s="7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I268" s="7" t="n"/>
       <c r="J268" s="7" t="n"/>
@@ -80504,14 +80196,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F269" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G269" s="8" t="n">
-        <v>46418</v>
-      </c>
+      <c r="F269" s="8" t="n"/>
+      <c r="G269" s="8" t="n"/>
       <c r="H269" s="7" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I269" s="7" t="n"/>
       <c r="J269" s="7" t="n"/>
@@ -80543,10 +80231,10 @@
         </is>
       </c>
       <c r="F270" s="8" t="n">
-        <v>46784</v>
+        <v>46753</v>
       </c>
       <c r="G270" s="8" t="n">
-        <v>46843</v>
+        <v>46904</v>
       </c>
       <c r="H270" s="7" t="n">
         <v>0.15</v>
@@ -80581,13 +80269,13 @@
         </is>
       </c>
       <c r="F271" s="8" t="n">
-        <v>46753</v>
+        <v>46784</v>
       </c>
       <c r="G271" s="8" t="n">
-        <v>46843</v>
+        <v>46873</v>
       </c>
       <c r="H271" s="7" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I271" s="7" t="n"/>
       <c r="J271" s="7" t="n"/>
@@ -80618,12 +80306,8 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F272" s="8" t="n">
-        <v>46722</v>
-      </c>
-      <c r="G272" s="8" t="n">
-        <v>46873</v>
-      </c>
+      <c r="F272" s="8" t="n"/>
+      <c r="G272" s="8" t="n"/>
       <c r="H272" s="7" t="n">
         <v>0.14</v>
       </c>
@@ -80657,13 +80341,13 @@
         </is>
       </c>
       <c r="F273" s="8" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="G273" s="8" t="n">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="H273" s="7" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="I273" s="7" t="n"/>
       <c r="J273" s="7" t="n"/>
@@ -80701,7 +80385,7 @@
         <v>46387</v>
       </c>
       <c r="H274" s="7" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="I274" s="7" t="n"/>
       <c r="J274" s="7" t="n"/>
@@ -80732,14 +80416,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F275" s="8" t="n">
-        <v>45870</v>
-      </c>
-      <c r="G275" s="8" t="n">
-        <v>46418</v>
-      </c>
+      <c r="F275" s="8" t="n"/>
+      <c r="G275" s="8" t="n"/>
       <c r="H275" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I275" s="7" t="n"/>
       <c r="J275" s="7" t="n"/>
@@ -80771,13 +80451,13 @@
         </is>
       </c>
       <c r="F276" s="8" t="n">
-        <v>46784</v>
+        <v>46813</v>
       </c>
       <c r="G276" s="8" t="n">
         <v>47057</v>
       </c>
       <c r="H276" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I276" s="7" t="n"/>
       <c r="J276" s="7" t="n"/>
@@ -80809,13 +80489,13 @@
         </is>
       </c>
       <c r="F277" s="8" t="n">
-        <v>46784</v>
+        <v>46813</v>
       </c>
       <c r="G277" s="8" t="n">
-        <v>47087</v>
+        <v>47118</v>
       </c>
       <c r="H277" s="7" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="I277" s="7" t="n"/>
       <c r="J277" s="7" t="n"/>
@@ -80846,14 +80526,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F278" s="8" t="n">
-        <v>46784</v>
-      </c>
-      <c r="G278" s="8" t="n">
-        <v>47057</v>
-      </c>
+      <c r="F278" s="8" t="n"/>
+      <c r="G278" s="8" t="n"/>
       <c r="H278" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="I278" s="7" t="n"/>
       <c r="J278" s="7" t="n"/>
@@ -80891,7 +80567,7 @@
         <v>47115</v>
       </c>
       <c r="H279" s="7" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="I279" s="7" t="n"/>
       <c r="J279" s="7" t="n"/>
@@ -80926,10 +80602,10 @@
         <v>46966</v>
       </c>
       <c r="G280" s="8" t="n">
-        <v>47146</v>
+        <v>47115</v>
       </c>
       <c r="H280" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I280" s="7" t="n"/>
       <c r="J280" s="7" t="n"/>
@@ -80960,14 +80636,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F281" s="8" t="n">
-        <v>46966</v>
-      </c>
-      <c r="G281" s="8" t="n">
-        <v>47115</v>
-      </c>
+      <c r="F281" s="8" t="n"/>
+      <c r="G281" s="8" t="n"/>
       <c r="H281" s="7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I281" s="7" t="n"/>
       <c r="J281" s="7" t="n"/>
@@ -81005,7 +80677,7 @@
         <v>46752</v>
       </c>
       <c r="H282" s="7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I282" s="7" t="n"/>
       <c r="J282" s="7" t="n"/>
@@ -81037,13 +80709,13 @@
         </is>
       </c>
       <c r="F283" s="8" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="G283" s="8" t="n">
         <v>46691</v>
       </c>
       <c r="H283" s="7" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I283" s="7" t="n"/>
       <c r="J283" s="7" t="n"/>
@@ -81074,14 +80746,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F284" s="8" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G284" s="8" t="n">
-        <v>46752</v>
-      </c>
+      <c r="F284" s="8" t="n"/>
+      <c r="G284" s="8" t="n"/>
       <c r="H284" s="7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I284" s="7" t="n"/>
       <c r="J284" s="7" t="n"/>
@@ -81113,13 +80781,13 @@
         </is>
       </c>
       <c r="F285" s="8" t="n">
-        <v>46419</v>
+        <v>46478</v>
       </c>
       <c r="G285" s="8" t="n">
-        <v>46934</v>
+        <v>46904</v>
       </c>
       <c r="H285" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I285" s="7" t="n"/>
       <c r="J285" s="7" t="n"/>
@@ -81151,13 +80819,13 @@
         </is>
       </c>
       <c r="F286" s="8" t="n">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="G286" s="8" t="n">
-        <v>46965</v>
+        <v>46904</v>
       </c>
       <c r="H286" s="7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I286" s="7" t="n"/>
       <c r="J286" s="7" t="n"/>
@@ -81188,14 +80856,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F287" s="8" t="n">
-        <v>46478</v>
-      </c>
-      <c r="G287" s="8" t="n">
-        <v>46934</v>
-      </c>
+      <c r="F287" s="8" t="n"/>
+      <c r="G287" s="8" t="n"/>
       <c r="H287" s="7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="I287" s="7" t="n"/>
       <c r="J287" s="7" t="n"/>
